--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="H134" s="5" t="inlineStr">
         <is>
-          <t>자극/활동 Factor: 짧은 안내형 마음챙김 vs 능동 대조 과제(프롬프트마다 무작위 배정); 매체: 스마트폰 앱; 결과: 반추; 부정 정서</t>
+          <t>자극/활동 Factor: 3분 오디오 안내 마음챙김 vs 능동 대조 과제(프롬프트마다 무작위 배정); 매체: 스마트폰 앱; 결과: 반추; 부정 정서</t>
         </is>
       </c>
       <c r="I134" s="5" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="K134" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="K198" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -14581,7 +14581,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>짧은 안내형 마음챙김(약 3분); 일상 반복</t>
+          <t>3분 오디오 안내 마음챙김; 일상 반복(하루 8회 × 10일)</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -4055,7 +4055,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 저자 원고본 확인(표지·Table 1–4 없음)</t>
+          <t>2026-10-23 / 저자 원고본 확인(UWE 저장소, 표지·Table 1–4 포함)</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 저자 원고본 확인(표지·Table 1–4 없음)</t>
+          <t>2026-10-23 / 저자 원고본 확인(UWE 저장소, 표지·Table 1–4 포함)</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / 저자 원고본 확인(표지·Table 1–4 없음)</t>
+          <t>2026-10-23 / 저자 원고본 확인(UWE 저장소, 표지·Table 1–4 포함)</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 저자 원고본 확인(표지·Table 1–4 없음)</t>
+          <t>2026-10-23 / 저자 원고본 확인(UWE 저장소, 표지·Table 1–4 포함)</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -4201,7 +4201,7 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>기전/Factor: 주의 회복; 심박 반응; 추출 대상: 인지 부하 후 자연 vs 도시 영상의 선택적 주의·심박 차이</t>
+          <t>기전/Factor: 주의 회복; 자율신경 각성(심박); 관찰 결과: 자연 영상 시청 중 심박이 더 낮았고 시청 뒤 공간 선택적 주의가 줄어, 낮은 각성이 주의 방식을 바꾼다고 해석</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>자극/활동 Factor: 인지 부하 후 자연/도시 환경 영상 시청; 매체: 동영상; 결과: 선택적 주의; 심박</t>
+          <t>자극/활동 Factor: 교정 과제 15분(인지 부하) 후 자연/도시 환경 영상 20분(15초 장면 80개) 시청; 매체: 동영상; 결과: 선택적 주의; 심박</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="H133" s="5" t="inlineStr">
         <is>
-          <t>자극/활동 Factor: 자연 환경 명상(ReST) vs 일반 마음챙김 과정; 매체: 실제 자연·다주 과정; 결과: 훈련 참여 지속·순응도</t>
+          <t>자극/활동 Factor: 정원 환경 5주 명상 과정(ReST) vs 실내 강의실 일반 마음챙김 과정; 매체: 실제 자연·다주 과정; 결과: 중도 탈락; 과제 수행</t>
         </is>
       </c>
       <c r="I133" s="5" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>측정 지표: 선택적 주의 과제; 심박; 결과요약: 원문 확보 후 기재</t>
+          <t>측정 지표: Posner 주의 정향 과제(반응시간); 심박 간격(IBI); 결과요약: 28명. 영상 시청 뒤 자연 영상 집단만 유효·무효 단서 간 반응시간 차이가 사라졌고(공간 선택적 주의 감소), 시청 중 심박은 도시 영상 집단보다 낮음(기저선 대비)</t>
         </is>
       </c>
       <c r="I195" s="6" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="K196" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>측정 지표: 훈련 순응도(세부 지표는 원문 확인 필요); 결과요약: 제목 기준 자연 명상 환경이 마음챙김 훈련 순응도를 높임</t>
+          <t>측정 지표: 과정 중도 탈락; 주별 과제 수행 기록; 결과요약: 무작위 배정 139명 중 탈락은 ReST 10%(7/68), 일반 마음챙김 27%(19/71)(p=.013)였고 과제 수행도 ReST에서 더 오래 유지. 회복성 지각과 상태 마음챙김이 차이를 매개</t>
         </is>
       </c>
       <c r="I197" s="6" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -13270,12 +13270,12 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>인지 부하 후 영상 시청이 선택적 주의·심박에 미치는 영향 비교. 정지 이미지·야외 보행과 매체가 다름</t>
+          <t>인지 부하 후 자연 영상 20분을 본 집단은 도시 영상 집단보다 시청 중 심박이 낮고 시청 뒤 공간 선택적 주의가 줄어듦(28명). 정지 이미지·야외 보행과 매체가 다름</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / Europe PMC 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
@@ -16198,12 +16198,12 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>자연 환경 명상이 마음챙김 훈련 순응도를 높인다고 보고(제목 기준). 당일 회복이 아니라 장기 참여 유지 근거</t>
+          <t>정원 환경 명상(ReST)은 실내 일반 마음챙김보다 중도 탈락이 적고(10% vs 27%) 과제 수행이 오래 유지됨. 당일 회복이 아니라 장기 참여 유지 근거</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>2026-10-23 / 원문·초록 미확인(36편 근거 시트 요약 기준)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -5921,7 +5921,7 @@
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H169" s="5" t="inlineStr">
         <is>
-          <t>측정 지표: 지각된 회복성; 새소리 연관; 결과요약: 새소리 종류와 개인 연상에 따라 지각이 달라짐</t>
+          <t>측정 지표: 지각된 회복성; 새소리 연관; 결과요약: 성인 20명 면담에서 새소리가 스트레스 회복·주의 회복과 가장 많이 연관된 자연 소리였으나 모든 새소리가 도움이 되지는 않았고, 지각은 새소리 종류와 개인 연상에 따라 달라짐</t>
         </is>
       </c>
       <c r="I169" s="5" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>초록 확인</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -1423,7 +1423,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 / 저널·PubMed 본문</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 / 저널·PubMed 본문</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 / 저널 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>기전/Factor: PFA; evolutionary assumption critique; 관찰 결과: 이론적 가정</t>
+          <t>기전/Factor: PFA; evolutionary assumption critique; 관찰 결과: 회복 반응을 진화적 적응으로 보는 SRT 가정에 실증·개념적 근거가 약하다고 보고 처리 유창성 모델 제안</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>기전/Factor: PSD; serene; refuge; prospect; 관찰 결과: 선호; 스트레스 관련 지각</t>
+          <t>기전/Factor: PSD; serene; refuge; prospect; 관찰 결과: 일반 선호는 Serene이 가장 높고, 스트레스와는 Refuge·Nature 선호가 가장 강하게 연관</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>기전/Factor: fascination; being away; extent; compatibility; 관찰 결과: Restorative component ratings</t>
+          <t>기전/Factor: fascination; being away; extent; compatibility; 관찰 결과: being away가 물리적·심리적 이탈 2요인으로 나뉜 5요인 구조, 자연 환경이 모든 요인에서 도시보다 높음</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 / 저널 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Scott, Duncan &amp; McCoy</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
-          <t>자극/활동 Factor: Five Senses; 안내 방식; 매체: 오감 주의 관찰·교육; 결과: 시험 불안(TAQ)</t>
+          <t>자극/활동 Factor: Five Senses(5-4-3-2-1 그라운딩); 40분 교육 세션; 매체: 오감 주의 관찰·교육; 결과: 시험 불안(TAQ)</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>자극/활동 Factor: fascination; being away; extent; compatibility; 매체: 자연/도시 이미지·영상에 대한 구성요소 평정; 결과: Restorative component ratings</t>
+          <t>자극/활동 Factor: fascination; being away; extent; compatibility; 매체: 자연/도시 환경 상상(연구 1, 238명)·환경 영상(연구 2, 157명)에 대한 구성요소 평정; 결과: Restorative component ratings</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="H146" s="5" t="inlineStr">
         <is>
-          <t>측정 지표: SART; Bayes factor; 결과요약: 자연 이미지의 주의력 회복 효과를 재현하지 못함</t>
+          <t>측정 지표: SART; Bayes factor; 결과요약: 자연 84명·도시 85명에서 자연 이미지의 주의력 회복 효과를 재현하지 못함(베이즈 분석도 영가설 지지)</t>
         </is>
       </c>
       <c r="I146" s="5" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 / 저널 초록</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Scott, Duncan &amp; McCoy</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="H151" s="5" t="inlineStr">
         <is>
-          <t>측정 지표: 시험 불안(TAQ); 결과요약: 사전사후 시험불안 감소 보고</t>
+          <t>측정 지표: 시험 불안(TAQ); 결과요약: 간호학생 94명 참여·48명 사전사후 완료. TAQ 평균 4.7점 감소(p&lt;.001), 고불안 비율 23%→4%(p=.03)</t>
         </is>
       </c>
       <c r="I151" s="5" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>이번 회차 원문 미재검증</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>2026-10-22 / 저널·PubMed 본문</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>자연 이미지의 주의력 회복 효과를 재현하지 못함</t>
+          <t>자연/도시 이미지 25장(각 6초) 시청 전후 SART 비교에서 자연 이미지의 주의력 회복 효과를 재현하지 못함(자연 84명·도시 85명)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-22 출판사/PubMed 근거 재확인(상세 수치 추가 정독)</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>자연 선호·회복 이론의 진화론적 가정 검토</t>
+          <t>SRT의 진화론적 가정을 비판적으로 검토하고, 자연 회복 반응을 처리 유창성으로 설명하는 대안 모델 제시</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>미확인/원문 정독 필요</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>지각된 자연 환경 특성의 주요 차원 도출</t>
+          <t>953명 우편 설문으로 8개 지각 차원 도출. Serene 선호가 가장 높고, 스트레스군에는 Refuge·Nature·Rich in Species 조합이 회복적일 수 있음</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>초록 확인</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Scott, Duncan &amp; McCoy</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -14346,12 +14346,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>사전사후 시험불안 감소 보고</t>
+          <t>간호학생 대상 40분 교육(5-4-3-2-1 오감 그라운딩) 뒤 시험 전후 TAQ 4.7점 감소(p&lt;.001). 대조군 없는 단일군 설계</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>기존 조사; 원문 재검토</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -15542,12 +15542,12 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>지각된 자연 환경 특성의 주요 차원 도출</t>
+          <t>953명 우편 설문으로 8개 지각 차원 도출. Serene 선호가 가장 높고, 스트레스군에는 Refuge·Nature·Rich in Species 조합이 회복적일 수 있음</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>미확인/원문 정독 필요</t>
+          <t>2026-10-23 / 원문 PDF 확인</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Chen et al.</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Chen et al.</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Fan &amp; Baharum</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Keenan et al.</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Chen et al.</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Fan &amp; Baharum</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Keenan et al.</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Fan &amp; Baharum</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Fan &amp; Baharum</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Chen et al.</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Keenan et al.</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -15279,7 +15279,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Fan &amp; Baharum</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>저자 원문 확인</t>
+          <t>Keenan et al.</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Stenzel et al.</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Wei et al.</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Macrynikola et al.</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Muhammad Khir et al.</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Macrynikola et al.</t>
         </is>
       </c>
       <c r="E181" s="6" t="n">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>저자 정보 원문 확인</t>
+          <t>Muhammad Khir et al.</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">

--- a/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
+++ b/LUMI_R_C_Research_2026-10-22/LUMI_R_C_논문목록_2026-10-22.xlsx
@@ -1089,7 +1089,11 @@
           <t>RNT의 정의·평가 도구</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>10.1017/S0033291725000017</t>
+        </is>
+      </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12017360/</t>
@@ -6789,7 +6793,11 @@
           <t>세션 기간·중재 조건</t>
         </is>
       </c>
-      <c r="I119" s="5" t="n"/>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>10.2147/PRBM.S437277</t>
+        </is>
+      </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10844009/</t>
@@ -14654,7 +14662,11 @@
           <t>미확인/원문 정독 필요</t>
         </is>
       </c>
-      <c r="K61" s="5" t="n"/>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>10.2147/PRBM.S437277</t>
+        </is>
+      </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
           <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10844009/</t>
